--- a/outputs/Block5_House_Distribution.xlsx
+++ b/outputs/Block5_House_Distribution.xlsx
@@ -453,13 +453,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>0.5513716620292705</v>
+        <v>1.026071324842432</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>0.4319867474853653</v>
+        <v>-0.03694832434740891</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -467,13 +467,13 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>0.7074963699328916</v>
+        <v>1.699906626866217</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3">
-        <v>0.2711498578856142</v>
+        <v>0.2820732968571464</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -481,13 +481,13 @@
         <v>6</v>
       </c>
       <c r="B4">
-        <v>7.820194910667125</v>
+        <v>10.0582691946606</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>-0.05622532387349466</v>
+        <v>-0.1648931557853732</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -495,13 +495,13 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>5.173756282914196</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>-0.3299114487681276</v>
+        <v>0.3545840920074594</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -509,13 +509,13 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>18.4418098343119</v>
+        <v>19.01148659179185</v>
       </c>
       <c r="C6">
         <v>19</v>
       </c>
       <c r="D6">
-        <v>0.001576418180540884</v>
+        <v>-0.2130202719963314</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -523,13 +523,13 @@
         <v>9</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>0.433187337447319</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -537,13 +537,13 @@
         <v>10</v>
       </c>
       <c r="B8">
-        <v>176.0063243272117</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="C8">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="D8">
-        <v>-0.3185762509098993</v>
+        <v>-0.4769462223457026</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -551,13 +551,13 @@
         <v>11</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>1.16567981478854</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>-0.1780367518371049</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -565,13 +565,13 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>3.990456585529889</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>0.263598624927845</v>
+        <v>-0.4401936139338187</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -579,13 +579,13 @@
         <v>13</v>
       </c>
       <c r="B11">
-        <v>3.02590709890818</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>0.1667393936326196</v>
+        <v>-0.5287224693580312</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -593,13 +593,13 @@
         <v>14</v>
       </c>
       <c r="B12">
-        <v>15.02106749310035</v>
+        <v>12.98388364583827</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D12">
-        <v>-0.06474072159816124</v>
+        <v>0.1478640668473066</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -607,13 +607,13 @@
         <v>15</v>
       </c>
       <c r="B13">
-        <v>4.233012499265572</v>
+        <v>3.808811132083866</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13">
-        <v>0.0364852031454248</v>
+        <v>0.229836946441103</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -621,13 +621,13 @@
         <v>16</v>
       </c>
       <c r="B14">
-        <v>17.90152433308469</v>
+        <v>15.00521451603779</v>
       </c>
       <c r="C14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D14">
-        <v>0.2381887384590158</v>
+        <v>0.1470436791808698</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -635,13 +635,13 @@
         <v>17</v>
       </c>
       <c r="B15">
-        <v>4.766317009415515</v>
+        <v>4.801946011202828</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>-0.4628661022370464</v>
+        <v>0.2467794257059026</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -649,13 +649,13 @@
         <v>18</v>
       </c>
       <c r="B16">
-        <v>182.3239848953666</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="C16">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="D16">
-        <v>0.2837991667507822</v>
+        <v>0.1918505851803616</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -663,13 +663,13 @@
         <v>19</v>
       </c>
       <c r="B17">
-        <v>3.696547591818899</v>
+        <v>4.035405960595082</v>
       </c>
       <c r="C17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>-0.4612043030804567</v>
+        <v>0.005541379936312207</v>
       </c>
     </row>
   </sheetData>
